--- a/docs/Project-Tracker.xlsx
+++ b/docs/Project-Tracker.xlsx
@@ -15,8 +15,8 @@
   </sheets>
   <definedNames>
     <definedName function="false" hidden="true" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">AI!$A$1:$I$25</definedName>
-    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">Backend!$A$1:$I$36</definedName>
-    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">Frontend!$A$1:$I$29</definedName>
+    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">Backend!$A$1:$I$39</definedName>
+    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">Frontend!$A$1:$I$31</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="634" uniqueCount="308">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="667" uniqueCount="323">
   <si>
     <t xml:space="preserve">AI Law Portal: Project Tracker</t>
   </si>
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Login and auth context</t>
   </si>
   <si>
-    <t xml:space="preserve">JWT stored client-side, protected routes, sign out</t>
+    <t xml:space="preserve">Animated split-screen sign-in with SVG illustration; JWT session, protected routes, sign out</t>
   </si>
   <si>
     <t xml:space="preserve">BE-04</t>
@@ -447,15 +447,36 @@
     <t xml:space="preserve">FE-28</t>
   </si>
   <si>
-    <t xml:space="preserve">User management UI (admin)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Create users, change roles</t>
+    <t xml:space="preserve">Admin panel: Team &amp; access</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Create logins (invite link or temporary password), change roles, disable/enable, reset links, search and filters</t>
   </si>
   <si>
     <t xml:space="preserve">BE-07</t>
   </si>
   <si>
+    <t xml:space="preserve">FE-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Invite activation (register) flow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paste invite link, verify, set name and password with strength meter, success animation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BE-36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FE-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">First-run firm setup</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Two-step: firm name, then first admin account; refused once any user exists</t>
+  </si>
+  <si>
     <t xml:space="preserve">BE-01</t>
   </si>
   <si>
@@ -510,10 +531,7 @@
     <t xml:space="preserve">User management API (admin)</t>
   </si>
   <si>
-    <t xml:space="preserve">Create/disable users, change roles (GET /auth/users list exists)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Role changes admin-only</t>
+    <t xml:space="preserve">List, create (invite or temp password), change role, disable/enable, reissue link; self-lockout and last-admin guards</t>
   </si>
   <si>
     <t xml:space="preserve">Clients API</t>
@@ -751,6 +769,33 @@
   </si>
   <si>
     <t xml:space="preserve">Docker-free local run today; add CI for lint, tests, build</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Firm setup and invite API</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/auth/setup, /auth/invite/{token}, /auth/accept-invite; tokens stored as SHA-256, single use, 7-day expiry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BE-37</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Email delivery of invite and reset links</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Today the admin copies the link; send it through EmailProvider</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Email integration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BE-38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Login rate limiting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Throttle repeated failed sign-ins per email and IP</t>
   </si>
   <si>
     <t xml:space="preserve">AI-01</t>
@@ -1094,16 +1139,20 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1111,7 +1160,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1123,7 +1172,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1135,11 +1184,11 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1507,302 +1556,302 @@
   <dimension ref="A1:G24"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="2" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="2" style="1" width="13"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E4" s="3" t="s">
+      <c r="D4" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="5" t="n">
+      <c r="B5" s="6" t="n">
         <f aca="false">COUNTIF(Frontend!$E:$E,"Done")</f>
-        <v>12</v>
-      </c>
-      <c r="C5" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="C5" s="6" t="n">
         <f aca="false">COUNTIF(Frontend!$E:$E,"In Progress")</f>
         <v>1</v>
       </c>
-      <c r="D5" s="5" t="n">
+      <c r="D5" s="6" t="n">
         <f aca="false">COUNTIF(Frontend!$E:$E,"Not Started")</f>
-        <v>15</v>
-      </c>
-      <c r="E5" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="E5" s="6" t="n">
         <f aca="false">COUNTIF(Frontend!$E:$E,"Blocked")</f>
         <v>0</v>
       </c>
-      <c r="F5" s="5" t="n">
+      <c r="F5" s="6" t="n">
         <f aca="false">SUM(B5:E5)</f>
-        <v>28</v>
-      </c>
-      <c r="G5" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="G5" s="7" t="n">
         <f aca="false">IF(F5=0,0,B5/F5)</f>
-        <v>0.428571428571429</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="5" t="n">
+      <c r="B6" s="6" t="n">
         <f aca="false">COUNTIF(Backend!$E:$E,"Done")</f>
-        <v>14</v>
-      </c>
-      <c r="C6" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="C6" s="6" t="n">
         <f aca="false">COUNTIF(Backend!$E:$E,"In Progress")</f>
         <v>0</v>
       </c>
-      <c r="D6" s="5" t="n">
+      <c r="D6" s="6" t="n">
         <f aca="false">COUNTIF(Backend!$E:$E,"Not Started")</f>
-        <v>20</v>
-      </c>
-      <c r="E6" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="E6" s="6" t="n">
         <f aca="false">COUNTIF(Backend!$E:$E,"Blocked")</f>
         <v>1</v>
       </c>
-      <c r="F6" s="5" t="n">
+      <c r="F6" s="6" t="n">
         <f aca="false">SUM(B6:E6)</f>
-        <v>35</v>
-      </c>
-      <c r="G6" s="6" t="n">
+        <v>38</v>
+      </c>
+      <c r="G6" s="7" t="n">
         <f aca="false">IF(F6=0,0,B6/F6)</f>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
+        <v>0.421052631578947</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="5" t="n">
+      <c r="B7" s="6" t="n">
         <f aca="false">COUNTIF(AI!$E:$E,"Done")</f>
         <v>8</v>
       </c>
-      <c r="C7" s="5" t="n">
+      <c r="C7" s="6" t="n">
         <f aca="false">COUNTIF(AI!$E:$E,"In Progress")</f>
         <v>0</v>
       </c>
-      <c r="D7" s="5" t="n">
+      <c r="D7" s="6" t="n">
         <f aca="false">COUNTIF(AI!$E:$E,"Not Started")</f>
         <v>16</v>
       </c>
-      <c r="E7" s="5" t="n">
+      <c r="E7" s="6" t="n">
         <f aca="false">COUNTIF(AI!$E:$E,"Blocked")</f>
         <v>0</v>
       </c>
-      <c r="F7" s="5" t="n">
+      <c r="F7" s="6" t="n">
         <f aca="false">SUM(B7:E7)</f>
         <v>24</v>
       </c>
-      <c r="G7" s="6" t="n">
+      <c r="G7" s="7" t="n">
         <f aca="false">IF(F7=0,0,B7/F7)</f>
         <v>0.333333333333333</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="7" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="8" t="n">
+      <c r="B8" s="9" t="n">
         <f aca="false">SUM(B5:B7)</f>
-        <v>34</v>
-      </c>
-      <c r="C8" s="8" t="n">
+        <v>39</v>
+      </c>
+      <c r="C8" s="9" t="n">
         <f aca="false">SUM(C5:C7)</f>
         <v>1</v>
       </c>
-      <c r="D8" s="8" t="n">
+      <c r="D8" s="9" t="n">
         <f aca="false">SUM(D5:D7)</f>
         <v>51</v>
       </c>
-      <c r="E8" s="8" t="n">
+      <c r="E8" s="9" t="n">
         <f aca="false">SUM(E5:E7)</f>
         <v>1</v>
       </c>
-      <c r="F8" s="8" t="n">
+      <c r="F8" s="9" t="n">
         <f aca="false">SUM(F5:F7)</f>
-        <v>87</v>
-      </c>
-      <c r="G8" s="9" t="n">
+        <v>92</v>
+      </c>
+      <c r="G8" s="10" t="n">
         <f aca="false">IF(F8=0,0,B8/F8)</f>
-        <v>0.390804597701149</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="10" t="s">
+        <v>0.423913043478261</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="11" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="D11" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="5" t="n">
+      <c r="B12" s="6" t="n">
         <f aca="false">COUNTIFS(Frontend!$B:$B,$A12,Frontend!$E:$E,"Done")+COUNTIFS(Backend!$B:$B,$A12,Backend!$E:$E,"Done")+COUNTIFS(AI!$B:$B,$A12,AI!$E:$E,"Done")</f>
         <v>6</v>
       </c>
-      <c r="C12" s="5" t="n">
+      <c r="C12" s="6" t="n">
         <f aca="false">COUNTIF(Frontend!$B:$B,$A12)+COUNTIF(Backend!$B:$B,$A12)+COUNTIF(AI!$B:$B,$A12)</f>
         <v>7</v>
       </c>
-      <c r="D12" s="6" t="n">
+      <c r="D12" s="7" t="n">
         <f aca="false">IF(C12=0,0,B12/C12)</f>
         <v>0.857142857142857</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="s">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B13" s="5" t="n">
+      <c r="B13" s="6" t="n">
         <f aca="false">COUNTIFS(Frontend!$B:$B,$A13,Frontend!$E:$E,"Done")+COUNTIFS(Backend!$B:$B,$A13,Backend!$E:$E,"Done")+COUNTIFS(AI!$B:$B,$A13,AI!$E:$E,"Done")</f>
-        <v>25</v>
-      </c>
-      <c r="C13" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="C13" s="6" t="n">
         <f aca="false">COUNTIF(Frontend!$B:$B,$A13)+COUNTIF(Backend!$B:$B,$A13)+COUNTIF(AI!$B:$B,$A13)</f>
-        <v>34</v>
-      </c>
-      <c r="D13" s="6" t="n">
+        <v>38</v>
+      </c>
+      <c r="D13" s="7" t="n">
         <f aca="false">IF(C13=0,0,B13/C13)</f>
-        <v>0.735294117647059</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="4" t="s">
+        <v>0.789473684210526</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="5" t="n">
+      <c r="B14" s="6" t="n">
         <f aca="false">COUNTIFS(Frontend!$B:$B,$A14,Frontend!$E:$E,"Done")+COUNTIFS(Backend!$B:$B,$A14,Backend!$E:$E,"Done")+COUNTIFS(AI!$B:$B,$A14,AI!$E:$E,"Done")</f>
         <v>0</v>
       </c>
-      <c r="C14" s="5" t="n">
+      <c r="C14" s="6" t="n">
         <f aca="false">COUNTIF(Frontend!$B:$B,$A14)+COUNTIF(Backend!$B:$B,$A14)+COUNTIF(AI!$B:$B,$A14)</f>
         <v>10</v>
       </c>
-      <c r="D14" s="6" t="n">
+      <c r="D14" s="7" t="n">
         <f aca="false">IF(C14=0,0,B14/C14)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="4" t="s">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B15" s="5" t="n">
+      <c r="B15" s="6" t="n">
         <f aca="false">COUNTIFS(Frontend!$B:$B,$A15,Frontend!$E:$E,"Done")+COUNTIFS(Backend!$B:$B,$A15,Backend!$E:$E,"Done")+COUNTIFS(AI!$B:$B,$A15,AI!$E:$E,"Done")</f>
         <v>0</v>
       </c>
-      <c r="C15" s="5" t="n">
+      <c r="C15" s="6" t="n">
         <f aca="false">COUNTIF(Frontend!$B:$B,$A15)+COUNTIF(Backend!$B:$B,$A15)+COUNTIF(AI!$B:$B,$A15)</f>
         <v>11</v>
       </c>
-      <c r="D15" s="6" t="n">
+      <c r="D15" s="7" t="n">
         <f aca="false">IF(C15=0,0,B15/C15)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="4" t="s">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B16" s="5" t="n">
+      <c r="B16" s="6" t="n">
         <f aca="false">COUNTIFS(Frontend!$B:$B,$A16,Frontend!$E:$E,"Done")+COUNTIFS(Backend!$B:$B,$A16,Backend!$E:$E,"Done")+COUNTIFS(AI!$B:$B,$A16,AI!$E:$E,"Done")</f>
         <v>0</v>
       </c>
-      <c r="C16" s="5" t="n">
+      <c r="C16" s="6" t="n">
         <f aca="false">COUNTIF(Frontend!$B:$B,$A16)+COUNTIF(Backend!$B:$B,$A16)+COUNTIF(AI!$B:$B,$A16)</f>
         <v>10</v>
       </c>
-      <c r="D16" s="6" t="n">
+      <c r="D16" s="7" t="n">
         <f aca="false">IF(C16=0,0,B16/C16)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="4" t="s">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B17" s="5" t="n">
+      <c r="B17" s="6" t="n">
         <f aca="false">COUNTIFS(Frontend!$B:$B,$A17,Frontend!$E:$E,"Done")+COUNTIFS(Backend!$B:$B,$A17,Backend!$E:$E,"Done")+COUNTIFS(AI!$B:$B,$A17,AI!$E:$E,"Done")</f>
         <v>3</v>
       </c>
-      <c r="C17" s="5" t="n">
+      <c r="C17" s="6" t="n">
         <f aca="false">COUNTIF(Frontend!$B:$B,$A17)+COUNTIF(Backend!$B:$B,$A17)+COUNTIF(AI!$B:$B,$A17)</f>
-        <v>15</v>
-      </c>
-      <c r="D17" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="D17" s="7" t="n">
         <f aca="false">IF(C17=0,0,B17/C17)</f>
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="10" t="s">
+        <v>0.1875</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="11" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="11" t="s">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="12" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="11" t="s">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="12" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="11" t="s">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="12" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="2" t="s">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="3" t="s">
         <v>24</v>
       </c>
     </row>
@@ -1822,741 +1871,791 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="58"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="13"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="H1" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="I1" s="12" t="s">
+      <c r="I1" s="13" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="13" t="s">
+    <row r="2" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="C2" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="D2" s="13" t="s">
+      <c r="D2" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="E2" s="13" t="s">
+      <c r="E2" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="G2" s="13"/>
-      <c r="H2" s="13"/>
-      <c r="I2" s="14"/>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="13" t="s">
+      <c r="F2" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="G2" s="14"/>
+      <c r="H2" s="14"/>
+      <c r="I2" s="15"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="D3" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="E3" s="13" t="s">
+      <c r="E3" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="G3" s="13"/>
-      <c r="H3" s="13"/>
-      <c r="I3" s="14"/>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="13" t="s">
+      <c r="F3" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="G3" s="14"/>
+      <c r="H3" s="14"/>
+      <c r="I3" s="15"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="13" t="s">
+      <c r="C4" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="13" t="s">
+      <c r="D4" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="E4" s="13" t="s">
+      <c r="E4" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="G4" s="13" t="s">
+      <c r="F4" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="G4" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="H4" s="13"/>
-      <c r="I4" s="14"/>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="13" t="s">
+      <c r="H4" s="14"/>
+      <c r="I4" s="15"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="C5" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="D5" s="13" t="s">
+      <c r="D5" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="E5" s="13" t="s">
+      <c r="E5" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="F5" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="G5" s="13" t="s">
+      <c r="F5" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="G5" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="H5" s="13"/>
-      <c r="I5" s="14"/>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="13" t="s">
+      <c r="H5" s="14"/>
+      <c r="I5" s="15"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="B6" s="13" t="s">
+      <c r="B6" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="13" t="s">
+      <c r="C6" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="D6" s="13" t="s">
+      <c r="D6" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="E6" s="13" t="s">
+      <c r="E6" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="F6" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="G6" s="13" t="s">
+      <c r="F6" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="G6" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="H6" s="13"/>
-      <c r="I6" s="14"/>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="13" t="s">
+      <c r="H6" s="14"/>
+      <c r="I6" s="15"/>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="B7" s="13" t="s">
+      <c r="B7" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="13" t="s">
+      <c r="C7" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="D7" s="13" t="s">
+      <c r="D7" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="E7" s="13" t="s">
+      <c r="E7" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="F7" s="13" t="s">
+      <c r="F7" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="G7" s="13" t="s">
+      <c r="G7" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="H7" s="13"/>
-      <c r="I7" s="14"/>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="13" t="s">
+      <c r="H7" s="14"/>
+      <c r="I7" s="15"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="B8" s="13" t="s">
+      <c r="B8" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="13" t="s">
+      <c r="C8" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="D8" s="13" t="s">
+      <c r="D8" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="E8" s="13" t="s">
+      <c r="E8" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="F8" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="G8" s="13" t="s">
+      <c r="F8" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="G8" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="H8" s="13"/>
-      <c r="I8" s="14"/>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="13" t="s">
+      <c r="H8" s="14"/>
+      <c r="I8" s="15"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="B9" s="13" t="s">
+      <c r="B9" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="13" t="s">
+      <c r="C9" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="D9" s="13" t="s">
+      <c r="D9" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="E9" s="13" t="s">
+      <c r="E9" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="F9" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="G9" s="13" t="s">
+      <c r="F9" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="G9" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="H9" s="13"/>
-      <c r="I9" s="14"/>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="13" t="s">
+      <c r="H9" s="14"/>
+      <c r="I9" s="15"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="B10" s="13" t="s">
+      <c r="B10" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="13" t="s">
+      <c r="C10" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="D10" s="13" t="s">
+      <c r="D10" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="E10" s="13" t="s">
+      <c r="E10" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="F10" s="13" t="s">
+      <c r="F10" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="G10" s="13" t="s">
+      <c r="G10" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="H10" s="13"/>
-      <c r="I10" s="14"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="13" t="s">
+      <c r="H10" s="14"/>
+      <c r="I10" s="15"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="B11" s="13" t="s">
+      <c r="B11" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="13" t="s">
+      <c r="C11" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="D11" s="13" t="s">
+      <c r="D11" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="E11" s="13" t="s">
+      <c r="E11" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="F11" s="13" t="s">
+      <c r="F11" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="G11" s="13" t="s">
+      <c r="G11" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="H11" s="13"/>
-      <c r="I11" s="14"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="13" t="s">
+      <c r="H11" s="14"/>
+      <c r="I11" s="15"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="B12" s="13" t="s">
+      <c r="B12" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C12" s="13" t="s">
+      <c r="C12" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="D12" s="13" t="s">
+      <c r="D12" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="E12" s="13" t="s">
+      <c r="E12" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="F12" s="13" t="s">
+      <c r="F12" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="G12" s="13" t="s">
+      <c r="G12" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="H12" s="13"/>
-      <c r="I12" s="14"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="13" t="s">
+      <c r="H12" s="14"/>
+      <c r="I12" s="15"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="B13" s="13" t="s">
+      <c r="B13" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="C13" s="13" t="s">
+      <c r="C13" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="D13" s="13" t="s">
+      <c r="D13" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="E13" s="13" t="s">
+      <c r="E13" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="F13" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="G13" s="13" t="s">
+      <c r="F13" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="G13" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="H13" s="13"/>
-      <c r="I13" s="14"/>
-    </row>
-    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="13" t="s">
+      <c r="H13" s="14"/>
+      <c r="I13" s="15"/>
+    </row>
+    <row r="14" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="B14" s="13" t="s">
+      <c r="B14" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="13" t="s">
+      <c r="C14" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="D14" s="13" t="s">
+      <c r="D14" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="E14" s="13" t="s">
+      <c r="E14" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="F14" s="13" t="s">
+      <c r="F14" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="G14" s="13" t="s">
+      <c r="G14" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="H14" s="13"/>
-      <c r="I14" s="14"/>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="13" t="s">
+      <c r="H14" s="14"/>
+      <c r="I14" s="15"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="14" t="s">
         <v>85</v>
       </c>
-      <c r="B15" s="13" t="s">
+      <c r="B15" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C15" s="13" t="s">
+      <c r="C15" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="D15" s="13" t="s">
+      <c r="D15" s="14" t="s">
         <v>87</v>
       </c>
-      <c r="E15" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="F15" s="13" t="s">
+      <c r="E15" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="F15" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="G15" s="13"/>
-      <c r="H15" s="13"/>
-      <c r="I15" s="14"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="13" t="s">
+      <c r="G15" s="14"/>
+      <c r="H15" s="14"/>
+      <c r="I15" s="15"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="14" t="s">
         <v>88</v>
       </c>
-      <c r="B16" s="13" t="s">
+      <c r="B16" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="C16" s="13" t="s">
+      <c r="C16" s="14" t="s">
         <v>89</v>
       </c>
-      <c r="D16" s="13" t="s">
+      <c r="D16" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="E16" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="F16" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="G16" s="13" t="s">
+      <c r="E16" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="F16" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="G16" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="H16" s="13"/>
-      <c r="I16" s="14"/>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="13" t="s">
+      <c r="H16" s="14"/>
+      <c r="I16" s="15"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="14" t="s">
         <v>92</v>
       </c>
-      <c r="B17" s="13" t="s">
+      <c r="B17" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="C17" s="13" t="s">
+      <c r="C17" s="14" t="s">
         <v>93</v>
       </c>
-      <c r="D17" s="13" t="s">
+      <c r="D17" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="E17" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="F17" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="G17" s="13" t="s">
+      <c r="E17" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="F17" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="G17" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="H17" s="13"/>
-      <c r="I17" s="14"/>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="13" t="s">
+      <c r="H17" s="14"/>
+      <c r="I17" s="15"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="14" t="s">
         <v>96</v>
       </c>
-      <c r="B18" s="13" t="s">
+      <c r="B18" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="C18" s="13" t="s">
+      <c r="C18" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="D18" s="13" t="s">
+      <c r="D18" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="E18" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="F18" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="G18" s="13" t="s">
+      <c r="E18" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="F18" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="G18" s="14" t="s">
         <v>99</v>
       </c>
-      <c r="H18" s="13"/>
-      <c r="I18" s="14"/>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="13" t="s">
+      <c r="H18" s="14"/>
+      <c r="I18" s="15"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="B19" s="13" t="s">
+      <c r="B19" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="C19" s="13" t="s">
+      <c r="C19" s="14" t="s">
         <v>101</v>
       </c>
-      <c r="D19" s="13" t="s">
+      <c r="D19" s="14" t="s">
         <v>102</v>
       </c>
-      <c r="E19" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="F19" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="G19" s="13" t="s">
+      <c r="E19" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="F19" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="G19" s="14" t="s">
         <v>103</v>
       </c>
-      <c r="H19" s="13"/>
-      <c r="I19" s="14"/>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="13" t="s">
+      <c r="H19" s="14"/>
+      <c r="I19" s="15"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="B20" s="13" t="s">
+      <c r="B20" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="C20" s="13" t="s">
+      <c r="C20" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="D20" s="13" t="s">
+      <c r="D20" s="14" t="s">
         <v>106</v>
       </c>
-      <c r="E20" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="F20" s="13" t="s">
+      <c r="E20" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="F20" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="G20" s="13" t="s">
+      <c r="G20" s="14" t="s">
         <v>107</v>
       </c>
-      <c r="H20" s="13"/>
-      <c r="I20" s="14"/>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="13" t="s">
+      <c r="H20" s="14"/>
+      <c r="I20" s="15"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="14" t="s">
         <v>108</v>
       </c>
-      <c r="B21" s="13" t="s">
+      <c r="B21" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="C21" s="13" t="s">
+      <c r="C21" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="D21" s="13" t="s">
+      <c r="D21" s="14" t="s">
         <v>110</v>
       </c>
-      <c r="E21" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="F21" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="G21" s="13" t="s">
+      <c r="E21" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="F21" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="G21" s="14" t="s">
         <v>111</v>
       </c>
-      <c r="H21" s="13"/>
-      <c r="I21" s="14"/>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="13" t="s">
+      <c r="H21" s="14"/>
+      <c r="I21" s="15"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="14" t="s">
         <v>112</v>
       </c>
-      <c r="B22" s="13" t="s">
+      <c r="B22" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="C22" s="13" t="s">
+      <c r="C22" s="14" t="s">
         <v>113</v>
       </c>
-      <c r="D22" s="13" t="s">
+      <c r="D22" s="14" t="s">
         <v>114</v>
       </c>
-      <c r="E22" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="F22" s="13" t="s">
+      <c r="E22" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="F22" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="G22" s="13" t="s">
+      <c r="G22" s="14" t="s">
         <v>115</v>
       </c>
-      <c r="H22" s="13"/>
-      <c r="I22" s="14"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="13" t="s">
+      <c r="H22" s="14"/>
+      <c r="I22" s="15"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="14" t="s">
         <v>116</v>
       </c>
-      <c r="B23" s="13" t="s">
+      <c r="B23" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="C23" s="13" t="s">
+      <c r="C23" s="14" t="s">
         <v>117</v>
       </c>
-      <c r="D23" s="13" t="s">
+      <c r="D23" s="14" t="s">
         <v>118</v>
       </c>
-      <c r="E23" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="F23" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="G23" s="13" t="s">
+      <c r="E23" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="F23" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="G23" s="14" t="s">
         <v>119</v>
       </c>
-      <c r="H23" s="13"/>
-      <c r="I23" s="14"/>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="13" t="s">
+      <c r="H23" s="14"/>
+      <c r="I23" s="15"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="B24" s="13" t="s">
+      <c r="B24" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="C24" s="13" t="s">
+      <c r="C24" s="14" t="s">
         <v>121</v>
       </c>
-      <c r="D24" s="13" t="s">
+      <c r="D24" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="E24" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="F24" s="13" t="s">
+      <c r="E24" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="F24" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="G24" s="13" t="s">
+      <c r="G24" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="H24" s="13"/>
-      <c r="I24" s="14"/>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="13" t="s">
+      <c r="H24" s="14"/>
+      <c r="I24" s="15"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="B25" s="13" t="s">
+      <c r="B25" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="C25" s="13" t="s">
+      <c r="C25" s="14" t="s">
         <v>125</v>
       </c>
-      <c r="D25" s="13" t="s">
+      <c r="D25" s="14" t="s">
         <v>126</v>
       </c>
-      <c r="E25" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="F25" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="G25" s="13" t="s">
+      <c r="E25" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="F25" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="G25" s="14" t="s">
         <v>127</v>
       </c>
-      <c r="H25" s="13"/>
-      <c r="I25" s="14"/>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="13" t="s">
+      <c r="H25" s="14"/>
+      <c r="I25" s="15"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="B26" s="13" t="s">
+      <c r="B26" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="C26" s="13" t="s">
+      <c r="C26" s="14" t="s">
         <v>129</v>
       </c>
-      <c r="D26" s="13"/>
-      <c r="E26" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="F26" s="13" t="s">
+      <c r="D26" s="14"/>
+      <c r="E26" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="F26" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="G26" s="13"/>
-      <c r="H26" s="13"/>
-      <c r="I26" s="14"/>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="13" t="s">
+      <c r="G26" s="14"/>
+      <c r="H26" s="14"/>
+      <c r="I26" s="15"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="14" t="s">
         <v>130</v>
       </c>
-      <c r="B27" s="13" t="s">
+      <c r="B27" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="C27" s="13" t="s">
+      <c r="C27" s="14" t="s">
         <v>131</v>
       </c>
-      <c r="D27" s="13" t="s">
+      <c r="D27" s="14" t="s">
         <v>132</v>
       </c>
-      <c r="E27" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="F27" s="13" t="s">
+      <c r="E27" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="F27" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="G27" s="13" t="s">
+      <c r="G27" s="14" t="s">
         <v>133</v>
       </c>
-      <c r="H27" s="13"/>
-      <c r="I27" s="14"/>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="13" t="s">
+      <c r="H27" s="14"/>
+      <c r="I27" s="15"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="14" t="s">
         <v>134</v>
       </c>
-      <c r="B28" s="13" t="s">
+      <c r="B28" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="C28" s="13" t="s">
+      <c r="C28" s="14" t="s">
         <v>135</v>
       </c>
-      <c r="D28" s="13" t="s">
+      <c r="D28" s="14" t="s">
         <v>136</v>
       </c>
-      <c r="E28" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="F28" s="13" t="s">
+      <c r="E28" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="F28" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="G28" s="13" t="s">
+      <c r="G28" s="14" t="s">
         <v>137</v>
       </c>
-      <c r="H28" s="13"/>
-      <c r="I28" s="14"/>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="13" t="s">
+      <c r="H28" s="14"/>
+      <c r="I28" s="15"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="14" t="s">
         <v>138</v>
       </c>
-      <c r="B29" s="13" t="s">
+      <c r="B29" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C29" s="13" t="s">
+      <c r="C29" s="14" t="s">
         <v>139</v>
       </c>
-      <c r="D29" s="13" t="s">
+      <c r="D29" s="14" t="s">
         <v>140</v>
       </c>
-      <c r="E29" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="F29" s="13" t="s">
+      <c r="E29" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="F29" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="G29" s="13" t="s">
+      <c r="G29" s="14" t="s">
         <v>141</v>
       </c>
-      <c r="H29" s="13"/>
-      <c r="I29" s="14"/>
+      <c r="H29" s="14"/>
+      <c r="I29" s="15"/>
+    </row>
+    <row r="30" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="14" t="s">
+        <v>142</v>
+      </c>
+      <c r="B30" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="C30" s="14" t="s">
+        <v>143</v>
+      </c>
+      <c r="D30" s="14" t="s">
+        <v>144</v>
+      </c>
+      <c r="E30" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="F30" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="G30" s="14" t="s">
+        <v>145</v>
+      </c>
+      <c r="H30" s="14"/>
+      <c r="I30" s="15"/>
+    </row>
+    <row r="31" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="14" t="s">
+        <v>146</v>
+      </c>
+      <c r="B31" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="C31" s="14" t="s">
+        <v>147</v>
+      </c>
+      <c r="D31" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="E31" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="F31" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="G31" s="14" t="s">
+        <v>145</v>
+      </c>
+      <c r="H31" s="14"/>
+      <c r="I31" s="15"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I29"/>
+  <autoFilter ref="A1:I31"/>
   <conditionalFormatting sqref="E2:E129">
     <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
       <formula>"Done"</formula>
@@ -2597,890 +2696,961 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I36"/>
+  <dimension ref="A1:I39"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="58"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="13"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="H1" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="I1" s="12" t="s">
+      <c r="I1" s="13" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="13" t="s">
-        <v>142</v>
-      </c>
-      <c r="B2" s="13" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="14" t="s">
+        <v>149</v>
+      </c>
+      <c r="B2" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="13" t="s">
-        <v>143</v>
-      </c>
-      <c r="D2" s="13" t="s">
-        <v>144</v>
-      </c>
-      <c r="E2" s="13" t="s">
+      <c r="C2" s="14" t="s">
+        <v>150</v>
+      </c>
+      <c r="D2" s="14" t="s">
+        <v>151</v>
+      </c>
+      <c r="E2" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="G2" s="13"/>
-      <c r="H2" s="13"/>
-      <c r="I2" s="14"/>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="13" t="s">
+      <c r="F2" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="G2" s="14"/>
+      <c r="H2" s="14"/>
+      <c r="I2" s="15"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>153</v>
+      </c>
+      <c r="D3" s="14" t="s">
+        <v>154</v>
+      </c>
+      <c r="E3" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="G3" s="14"/>
+      <c r="H3" s="14"/>
+      <c r="I3" s="15"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>156</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>157</v>
+      </c>
+      <c r="E4" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="F4" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="G4" s="14" t="s">
+        <v>158</v>
+      </c>
+      <c r="H4" s="14"/>
+      <c r="I4" s="15"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>159</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>160</v>
+      </c>
+      <c r="E5" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="F5" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="G5" s="14"/>
+      <c r="H5" s="14"/>
+      <c r="I5" s="15"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>162</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>163</v>
+      </c>
+      <c r="E6" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="F6" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="G6" s="14"/>
+      <c r="H6" s="14"/>
+      <c r="I6" s="15"/>
+    </row>
+    <row r="7" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>164</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>165</v>
+      </c>
+      <c r="E7" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="F7" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="G7" s="14"/>
+      <c r="H7" s="14"/>
+      <c r="I7" s="15"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>166</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>167</v>
+      </c>
+      <c r="E8" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="F8" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="G8" s="14"/>
+      <c r="H8" s="14"/>
+      <c r="I8" s="15"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>168</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="E9" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="F9" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="G9" s="14"/>
+      <c r="H9" s="14"/>
+      <c r="I9" s="15"/>
+    </row>
+    <row r="10" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>170</v>
+      </c>
+      <c r="D10" s="14" t="s">
+        <v>171</v>
+      </c>
+      <c r="E10" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="F10" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="G10" s="14" t="s">
+        <v>172</v>
+      </c>
+      <c r="H10" s="14"/>
+      <c r="I10" s="15"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="D11" s="14" t="s">
+        <v>174</v>
+      </c>
+      <c r="E11" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="F11" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="G11" s="14"/>
+      <c r="H11" s="14"/>
+      <c r="I11" s="15"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="B12" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="D12" s="14" t="s">
+        <v>176</v>
+      </c>
+      <c r="E12" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="F12" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="G12" s="14"/>
+      <c r="H12" s="14"/>
+      <c r="I12" s="15"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="B13" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="C13" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="D13" s="14" t="s">
+        <v>178</v>
+      </c>
+      <c r="E13" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="F13" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="G13" s="14"/>
+      <c r="H13" s="14"/>
+      <c r="I13" s="15"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="14" t="s">
+        <v>179</v>
+      </c>
+      <c r="B14" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="D14" s="14" t="s">
+        <v>181</v>
+      </c>
+      <c r="E14" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="G14" s="14" t="s">
+        <v>182</v>
+      </c>
+      <c r="H14" s="14"/>
+      <c r="I14" s="15"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="14" t="s">
+        <v>183</v>
+      </c>
+      <c r="B15" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="C15" s="14" t="s">
+        <v>184</v>
+      </c>
+      <c r="D15" s="14" t="s">
+        <v>185</v>
+      </c>
+      <c r="E15" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="F15" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="G15" s="14" t="s">
+        <v>186</v>
+      </c>
+      <c r="H15" s="14"/>
+      <c r="I15" s="15"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="B16" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16" s="14" t="s">
+        <v>187</v>
+      </c>
+      <c r="D16" s="14" t="s">
+        <v>188</v>
+      </c>
+      <c r="E16" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="F16" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="G16" s="14"/>
+      <c r="H16" s="14"/>
+      <c r="I16" s="15"/>
+    </row>
+    <row r="17" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="14" t="s">
+        <v>189</v>
+      </c>
+      <c r="B17" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="C17" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="D17" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="E17" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="F17" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="G17" s="14" t="s">
+        <v>192</v>
+      </c>
+      <c r="H17" s="14"/>
+      <c r="I17" s="15"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="14" t="s">
+        <v>193</v>
+      </c>
+      <c r="B18" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="C18" s="14" t="s">
+        <v>194</v>
+      </c>
+      <c r="D18" s="14" t="s">
+        <v>195</v>
+      </c>
+      <c r="E18" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="F18" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="G18" s="14"/>
+      <c r="H18" s="14"/>
+      <c r="I18" s="15"/>
+    </row>
+    <row r="19" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="14" t="s">
+        <v>196</v>
+      </c>
+      <c r="B19" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19" s="14" t="s">
+        <v>197</v>
+      </c>
+      <c r="D19" s="14" t="s">
+        <v>198</v>
+      </c>
+      <c r="E19" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="F19" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="G19" s="14" t="s">
+        <v>199</v>
+      </c>
+      <c r="H19" s="14"/>
+      <c r="I19" s="15"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="14" t="s">
+        <v>200</v>
+      </c>
+      <c r="B20" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" s="14" t="s">
+        <v>201</v>
+      </c>
+      <c r="D20" s="14" t="s">
+        <v>202</v>
+      </c>
+      <c r="E20" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="F20" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="G20" s="14" t="s">
+        <v>196</v>
+      </c>
+      <c r="H20" s="14"/>
+      <c r="I20" s="15"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="14" t="s">
+        <v>203</v>
+      </c>
+      <c r="B21" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="C21" s="14" t="s">
+        <v>204</v>
+      </c>
+      <c r="D21" s="14" t="s">
+        <v>205</v>
+      </c>
+      <c r="E21" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="F21" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="G21" s="14" t="s">
+        <v>200</v>
+      </c>
+      <c r="H21" s="14"/>
+      <c r="I21" s="15"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="14" t="s">
+        <v>206</v>
+      </c>
+      <c r="B22" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="C22" s="14" t="s">
+        <v>207</v>
+      </c>
+      <c r="D22" s="14" t="s">
+        <v>208</v>
+      </c>
+      <c r="E22" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="F22" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="G22" s="14" t="s">
+        <v>209</v>
+      </c>
+      <c r="H22" s="14"/>
+      <c r="I22" s="15"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="14" t="s">
+        <v>210</v>
+      </c>
+      <c r="B23" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="C23" s="14" t="s">
+        <v>211</v>
+      </c>
+      <c r="D23" s="14" t="s">
+        <v>212</v>
+      </c>
+      <c r="E23" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="F23" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="G23" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="H23" s="14"/>
+      <c r="I23" s="15"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="B24" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="C24" s="14" t="s">
+        <v>213</v>
+      </c>
+      <c r="D24" s="14" t="s">
+        <v>214</v>
+      </c>
+      <c r="E24" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="F24" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="G24" s="14"/>
+      <c r="H24" s="14"/>
+      <c r="I24" s="15"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="B25" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="C25" s="14" t="s">
+        <v>215</v>
+      </c>
+      <c r="D25" s="14" t="s">
+        <v>216</v>
+      </c>
+      <c r="E25" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="F25" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="G25" s="14"/>
+      <c r="H25" s="14"/>
+      <c r="I25" s="15"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="B26" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="C26" s="14" t="s">
+        <v>217</v>
+      </c>
+      <c r="D26" s="14" t="s">
+        <v>218</v>
+      </c>
+      <c r="E26" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="F26" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="G26" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="H26" s="14"/>
+      <c r="I26" s="15"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="14" t="s">
+        <v>219</v>
+      </c>
+      <c r="B27" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="C27" s="14" t="s">
+        <v>220</v>
+      </c>
+      <c r="D27" s="14" t="s">
+        <v>221</v>
+      </c>
+      <c r="E27" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="F27" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="G27" s="14"/>
+      <c r="H27" s="14"/>
+      <c r="I27" s="15"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="B28" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="C28" s="14" t="s">
+        <v>222</v>
+      </c>
+      <c r="D28" s="14" t="s">
+        <v>223</v>
+      </c>
+      <c r="E28" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="F28" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="G28" s="14" t="s">
+        <v>219</v>
+      </c>
+      <c r="H28" s="14"/>
+      <c r="I28" s="15"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="14" t="s">
+        <v>224</v>
+      </c>
+      <c r="B29" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C29" s="14" t="s">
+        <v>225</v>
+      </c>
+      <c r="D29" s="14" t="s">
+        <v>226</v>
+      </c>
+      <c r="E29" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="F29" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="G29" s="14" t="s">
+        <v>227</v>
+      </c>
+      <c r="H29" s="14"/>
+      <c r="I29" s="15"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="14" t="s">
+        <v>228</v>
+      </c>
+      <c r="B30" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C30" s="14" t="s">
+        <v>229</v>
+      </c>
+      <c r="D30" s="14" t="s">
+        <v>230</v>
+      </c>
+      <c r="E30" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="F30" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="G30" s="14" t="s">
+        <v>224</v>
+      </c>
+      <c r="H30" s="14"/>
+      <c r="I30" s="15"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="14" t="s">
+        <v>231</v>
+      </c>
+      <c r="B31" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C31" s="14" t="s">
+        <v>232</v>
+      </c>
+      <c r="D31" s="14" t="s">
+        <v>233</v>
+      </c>
+      <c r="E31" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="F31" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="G31" s="14" t="s">
+        <v>224</v>
+      </c>
+      <c r="H31" s="14"/>
+      <c r="I31" s="15"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="B32" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="C32" s="14" t="s">
+        <v>234</v>
+      </c>
+      <c r="D32" s="14" t="s">
+        <v>235</v>
+      </c>
+      <c r="E32" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="F32" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="G32" s="14"/>
+      <c r="H32" s="14"/>
+      <c r="I32" s="15"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="14" t="s">
+        <v>236</v>
+      </c>
+      <c r="B33" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="C33" s="14" t="s">
+        <v>237</v>
+      </c>
+      <c r="D33" s="14" t="s">
+        <v>238</v>
+      </c>
+      <c r="E33" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="F33" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="G33" s="14" t="s">
+        <v>239</v>
+      </c>
+      <c r="H33" s="14"/>
+      <c r="I33" s="15"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="B34" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="C34" s="14" t="s">
+        <v>240</v>
+      </c>
+      <c r="D34" s="14" t="s">
+        <v>241</v>
+      </c>
+      <c r="E34" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="F34" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="G34" s="14"/>
+      <c r="H34" s="14"/>
+      <c r="I34" s="15"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="14" t="s">
+        <v>137</v>
+      </c>
+      <c r="B35" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="C35" s="14" t="s">
+        <v>242</v>
+      </c>
+      <c r="D35" s="14" t="s">
+        <v>243</v>
+      </c>
+      <c r="E35" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="F35" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="G35" s="14"/>
+      <c r="H35" s="14"/>
+      <c r="I35" s="15"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="14" t="s">
+        <v>244</v>
+      </c>
+      <c r="B36" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="C36" s="14" t="s">
+        <v>245</v>
+      </c>
+      <c r="D36" s="14" t="s">
+        <v>246</v>
+      </c>
+      <c r="E36" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="F36" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="G36" s="14"/>
+      <c r="H36" s="14"/>
+      <c r="I36" s="15"/>
+    </row>
+    <row r="37" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="14" t="s">
         <v>145</v>
       </c>
-      <c r="B3" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" s="13" t="s">
-        <v>146</v>
-      </c>
-      <c r="D3" s="13" t="s">
-        <v>147</v>
-      </c>
-      <c r="E3" s="13" t="s">
+      <c r="B37" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="C37" s="14" t="s">
+        <v>247</v>
+      </c>
+      <c r="D37" s="14" t="s">
+        <v>248</v>
+      </c>
+      <c r="E37" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="G3" s="13"/>
-      <c r="H3" s="13"/>
-      <c r="I3" s="14"/>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="13" t="s">
-        <v>148</v>
-      </c>
-      <c r="B4" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" s="13" t="s">
-        <v>149</v>
-      </c>
-      <c r="D4" s="13" t="s">
-        <v>150</v>
-      </c>
-      <c r="E4" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="F4" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="G4" s="13" t="s">
-        <v>151</v>
-      </c>
-      <c r="H4" s="13"/>
-      <c r="I4" s="14"/>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="B5" s="13" t="s">
+      <c r="F37" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="G37" s="14"/>
+      <c r="H37" s="14"/>
+      <c r="I37" s="15"/>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="14" t="s">
+        <v>249</v>
+      </c>
+      <c r="B38" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="C38" s="14" t="s">
+        <v>250</v>
+      </c>
+      <c r="D38" s="14" t="s">
+        <v>251</v>
+      </c>
+      <c r="E38" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="F38" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="G38" s="14" t="s">
+        <v>252</v>
+      </c>
+      <c r="H38" s="14"/>
+      <c r="I38" s="15"/>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="14" t="s">
+        <v>253</v>
+      </c>
+      <c r="B39" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="13" t="s">
-        <v>152</v>
-      </c>
-      <c r="D5" s="13" t="s">
-        <v>153</v>
-      </c>
-      <c r="E5" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="F5" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="G5" s="13"/>
-      <c r="H5" s="13"/>
-      <c r="I5" s="14"/>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="13" t="s">
-        <v>154</v>
-      </c>
-      <c r="B6" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="D6" s="13" t="s">
-        <v>156</v>
-      </c>
-      <c r="E6" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="F6" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="G6" s="13"/>
-      <c r="H6" s="13"/>
-      <c r="I6" s="14"/>
-    </row>
-    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="B7" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="13" t="s">
-        <v>157</v>
-      </c>
-      <c r="D7" s="13" t="s">
-        <v>158</v>
-      </c>
-      <c r="E7" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="F7" s="13" t="s">
+      <c r="C39" s="14" t="s">
+        <v>254</v>
+      </c>
+      <c r="D39" s="14" t="s">
+        <v>255</v>
+      </c>
+      <c r="E39" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="F39" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="G7" s="13"/>
-      <c r="H7" s="13"/>
-      <c r="I7" s="14"/>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="13" t="s">
-        <v>141</v>
-      </c>
-      <c r="B8" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="C8" s="13" t="s">
-        <v>159</v>
-      </c>
-      <c r="D8" s="13" t="s">
-        <v>160</v>
-      </c>
-      <c r="E8" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="F8" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="G8" s="13" t="s">
-        <v>161</v>
-      </c>
-      <c r="H8" s="13"/>
-      <c r="I8" s="14"/>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="B9" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="C9" s="13" t="s">
-        <v>162</v>
-      </c>
-      <c r="D9" s="13" t="s">
-        <v>163</v>
-      </c>
-      <c r="E9" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="F9" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="G9" s="13"/>
-      <c r="H9" s="13"/>
-      <c r="I9" s="14"/>
-    </row>
-    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="B10" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="C10" s="13" t="s">
-        <v>164</v>
-      </c>
-      <c r="D10" s="13" t="s">
-        <v>165</v>
-      </c>
-      <c r="E10" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="F10" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="G10" s="13" t="s">
-        <v>166</v>
-      </c>
-      <c r="H10" s="13"/>
-      <c r="I10" s="14"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="B11" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="C11" s="13" t="s">
-        <v>167</v>
-      </c>
-      <c r="D11" s="13" t="s">
-        <v>168</v>
-      </c>
-      <c r="E11" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="F11" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="G11" s="13"/>
-      <c r="H11" s="13"/>
-      <c r="I11" s="14"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="B12" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="C12" s="13" t="s">
-        <v>169</v>
-      </c>
-      <c r="D12" s="13" t="s">
-        <v>170</v>
-      </c>
-      <c r="E12" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="F12" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="G12" s="13"/>
-      <c r="H12" s="13"/>
-      <c r="I12" s="14"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="B13" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="C13" s="13" t="s">
-        <v>171</v>
-      </c>
-      <c r="D13" s="13" t="s">
-        <v>172</v>
-      </c>
-      <c r="E13" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="F13" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="G13" s="13"/>
-      <c r="H13" s="13"/>
-      <c r="I13" s="14"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="13" t="s">
-        <v>173</v>
-      </c>
-      <c r="B14" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="C14" s="13" t="s">
-        <v>174</v>
-      </c>
-      <c r="D14" s="13" t="s">
-        <v>175</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="F14" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="G14" s="13" t="s">
-        <v>176</v>
-      </c>
-      <c r="H14" s="13"/>
-      <c r="I14" s="14"/>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="13" t="s">
-        <v>177</v>
-      </c>
-      <c r="B15" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="C15" s="13" t="s">
-        <v>178</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>179</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="F15" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="G15" s="13" t="s">
-        <v>180</v>
-      </c>
-      <c r="H15" s="13"/>
-      <c r="I15" s="14"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="B16" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="C16" s="13" t="s">
-        <v>181</v>
-      </c>
-      <c r="D16" s="13" t="s">
-        <v>182</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="F16" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="G16" s="13"/>
-      <c r="H16" s="13"/>
-      <c r="I16" s="14"/>
-    </row>
-    <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="13" t="s">
-        <v>183</v>
-      </c>
-      <c r="B17" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="C17" s="13" t="s">
-        <v>184</v>
-      </c>
-      <c r="D17" s="13" t="s">
-        <v>185</v>
-      </c>
-      <c r="E17" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="F17" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="G17" s="13" t="s">
-        <v>186</v>
-      </c>
-      <c r="H17" s="13"/>
-      <c r="I17" s="14"/>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="13" t="s">
-        <v>187</v>
-      </c>
-      <c r="B18" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="C18" s="13" t="s">
-        <v>188</v>
-      </c>
-      <c r="D18" s="13" t="s">
-        <v>189</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="F18" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="G18" s="13"/>
-      <c r="H18" s="13"/>
-      <c r="I18" s="14"/>
-    </row>
-    <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="13" t="s">
-        <v>190</v>
-      </c>
-      <c r="B19" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="C19" s="13" t="s">
-        <v>191</v>
-      </c>
-      <c r="D19" s="13" t="s">
+      <c r="G39" s="14" t="s">
         <v>192</v>
       </c>
-      <c r="E19" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="F19" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="G19" s="13" t="s">
-        <v>193</v>
-      </c>
-      <c r="H19" s="13"/>
-      <c r="I19" s="14"/>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="13" t="s">
-        <v>194</v>
-      </c>
-      <c r="B20" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="C20" s="13" t="s">
-        <v>195</v>
-      </c>
-      <c r="D20" s="13" t="s">
-        <v>196</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="F20" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="G20" s="13" t="s">
-        <v>190</v>
-      </c>
-      <c r="H20" s="13"/>
-      <c r="I20" s="14"/>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="13" t="s">
-        <v>197</v>
-      </c>
-      <c r="B21" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="C21" s="13" t="s">
-        <v>198</v>
-      </c>
-      <c r="D21" s="13" t="s">
-        <v>199</v>
-      </c>
-      <c r="E21" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="F21" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="G21" s="13" t="s">
-        <v>194</v>
-      </c>
-      <c r="H21" s="13"/>
-      <c r="I21" s="14"/>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="13" t="s">
-        <v>200</v>
-      </c>
-      <c r="B22" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="C22" s="13" t="s">
-        <v>201</v>
-      </c>
-      <c r="D22" s="13" t="s">
-        <v>202</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="F22" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="G22" s="13" t="s">
-        <v>203</v>
-      </c>
-      <c r="H22" s="13"/>
-      <c r="I22" s="14"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="13" t="s">
-        <v>204</v>
-      </c>
-      <c r="B23" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="C23" s="13" t="s">
-        <v>205</v>
-      </c>
-      <c r="D23" s="13" t="s">
-        <v>206</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="F23" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="G23" s="13" t="s">
-        <v>95</v>
-      </c>
-      <c r="H23" s="13"/>
-      <c r="I23" s="14"/>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="13" t="s">
-        <v>99</v>
-      </c>
-      <c r="B24" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="C24" s="13" t="s">
-        <v>207</v>
-      </c>
-      <c r="D24" s="13" t="s">
-        <v>208</v>
-      </c>
-      <c r="E24" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="F24" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="G24" s="13"/>
-      <c r="H24" s="13"/>
-      <c r="I24" s="14"/>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="13" t="s">
-        <v>103</v>
-      </c>
-      <c r="B25" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="C25" s="13" t="s">
-        <v>209</v>
-      </c>
-      <c r="D25" s="13" t="s">
-        <v>210</v>
-      </c>
-      <c r="E25" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="F25" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="G25" s="13"/>
-      <c r="H25" s="13"/>
-      <c r="I25" s="14"/>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="13" t="s">
-        <v>107</v>
-      </c>
-      <c r="B26" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="C26" s="13" t="s">
-        <v>211</v>
-      </c>
-      <c r="D26" s="13" t="s">
-        <v>212</v>
-      </c>
-      <c r="E26" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="F26" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="G26" s="13" t="s">
-        <v>103</v>
-      </c>
-      <c r="H26" s="13"/>
-      <c r="I26" s="14"/>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="13" t="s">
-        <v>213</v>
-      </c>
-      <c r="B27" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="C27" s="13" t="s">
-        <v>214</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>215</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="F27" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="G27" s="13"/>
-      <c r="H27" s="13"/>
-      <c r="I27" s="14"/>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="13" t="s">
-        <v>115</v>
-      </c>
-      <c r="B28" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="C28" s="13" t="s">
-        <v>216</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>217</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="F28" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="G28" s="13" t="s">
-        <v>213</v>
-      </c>
-      <c r="H28" s="13"/>
-      <c r="I28" s="14"/>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="13" t="s">
-        <v>218</v>
-      </c>
-      <c r="B29" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="C29" s="13" t="s">
-        <v>219</v>
-      </c>
-      <c r="D29" s="13" t="s">
-        <v>220</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="F29" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="G29" s="13" t="s">
-        <v>221</v>
-      </c>
-      <c r="H29" s="13"/>
-      <c r="I29" s="14"/>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="13" t="s">
-        <v>222</v>
-      </c>
-      <c r="B30" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="C30" s="13" t="s">
-        <v>223</v>
-      </c>
-      <c r="D30" s="13" t="s">
-        <v>224</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="F30" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="G30" s="13" t="s">
-        <v>218</v>
-      </c>
-      <c r="H30" s="13"/>
-      <c r="I30" s="14"/>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="13" t="s">
-        <v>225</v>
-      </c>
-      <c r="B31" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="C31" s="13" t="s">
-        <v>226</v>
-      </c>
-      <c r="D31" s="13" t="s">
-        <v>227</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="F31" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="G31" s="13" t="s">
-        <v>218</v>
-      </c>
-      <c r="H31" s="13"/>
-      <c r="I31" s="14"/>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="13" t="s">
-        <v>123</v>
-      </c>
-      <c r="B32" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="C32" s="13" t="s">
-        <v>228</v>
-      </c>
-      <c r="D32" s="13" t="s">
-        <v>229</v>
-      </c>
-      <c r="E32" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="F32" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="G32" s="13"/>
-      <c r="H32" s="13"/>
-      <c r="I32" s="14"/>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="13" t="s">
-        <v>230</v>
-      </c>
-      <c r="B33" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="C33" s="13" t="s">
-        <v>231</v>
-      </c>
-      <c r="D33" s="13" t="s">
-        <v>232</v>
-      </c>
-      <c r="E33" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="F33" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="G33" s="13" t="s">
-        <v>233</v>
-      </c>
-      <c r="H33" s="13"/>
-      <c r="I33" s="14"/>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="13" t="s">
-        <v>133</v>
-      </c>
-      <c r="B34" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="C34" s="13" t="s">
-        <v>234</v>
-      </c>
-      <c r="D34" s="13" t="s">
-        <v>235</v>
-      </c>
-      <c r="E34" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="F34" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="G34" s="13"/>
-      <c r="H34" s="13"/>
-      <c r="I34" s="14"/>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="13" t="s">
-        <v>137</v>
-      </c>
-      <c r="B35" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="C35" s="13" t="s">
-        <v>236</v>
-      </c>
-      <c r="D35" s="13" t="s">
-        <v>237</v>
-      </c>
-      <c r="E35" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="F35" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="G35" s="13"/>
-      <c r="H35" s="13"/>
-      <c r="I35" s="14"/>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="13" t="s">
-        <v>238</v>
-      </c>
-      <c r="B36" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="C36" s="13" t="s">
-        <v>239</v>
-      </c>
-      <c r="D36" s="13" t="s">
-        <v>240</v>
-      </c>
-      <c r="E36" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="F36" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="G36" s="13"/>
-      <c r="H36" s="13"/>
-      <c r="I36" s="14"/>
+      <c r="H39" s="14"/>
+      <c r="I39" s="15"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I36"/>
+  <autoFilter ref="A1:I39"/>
   <conditionalFormatting sqref="E2:E136">
     <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
       <formula>"Done"</formula>
@@ -3524,629 +3694,629 @@
   <dimension ref="A1:I25"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="58"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="13"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="H1" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="I1" s="12" t="s">
+      <c r="I1" s="13" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="13" t="s">
-        <v>241</v>
-      </c>
-      <c r="B2" s="13" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="14" t="s">
+        <v>256</v>
+      </c>
+      <c r="B2" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="13" t="s">
-        <v>242</v>
-      </c>
-      <c r="D2" s="13" t="s">
-        <v>243</v>
-      </c>
-      <c r="E2" s="13" t="s">
+      <c r="C2" s="14" t="s">
+        <v>257</v>
+      </c>
+      <c r="D2" s="14" t="s">
+        <v>258</v>
+      </c>
+      <c r="E2" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="G2" s="13"/>
-      <c r="H2" s="13"/>
-      <c r="I2" s="14"/>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="13" t="s">
-        <v>244</v>
-      </c>
-      <c r="B3" s="13" t="s">
+      <c r="F2" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="G2" s="14"/>
+      <c r="H2" s="14"/>
+      <c r="I2" s="15"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="14" t="s">
+        <v>259</v>
+      </c>
+      <c r="B3" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="13" t="s">
-        <v>245</v>
-      </c>
-      <c r="D3" s="13" t="s">
-        <v>246</v>
-      </c>
-      <c r="E3" s="13" t="s">
+      <c r="C3" s="14" t="s">
+        <v>260</v>
+      </c>
+      <c r="D3" s="14" t="s">
+        <v>261</v>
+      </c>
+      <c r="E3" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="G3" s="13" t="s">
-        <v>247</v>
-      </c>
-      <c r="H3" s="13"/>
-      <c r="I3" s="14"/>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="13" t="s">
-        <v>248</v>
-      </c>
-      <c r="B4" s="13" t="s">
+      <c r="F3" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="G3" s="14" t="s">
+        <v>262</v>
+      </c>
+      <c r="H3" s="14"/>
+      <c r="I3" s="15"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="14" t="s">
+        <v>263</v>
+      </c>
+      <c r="B4" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="13" t="s">
-        <v>249</v>
-      </c>
-      <c r="D4" s="13" t="s">
-        <v>250</v>
-      </c>
-      <c r="E4" s="13" t="s">
+      <c r="C4" s="14" t="s">
+        <v>264</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>265</v>
+      </c>
+      <c r="E4" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="G4" s="13" t="s">
-        <v>247</v>
-      </c>
-      <c r="H4" s="13"/>
-      <c r="I4" s="14"/>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="13" t="s">
-        <v>233</v>
-      </c>
-      <c r="B5" s="13" t="s">
+      <c r="F4" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="G4" s="14" t="s">
+        <v>262</v>
+      </c>
+      <c r="H4" s="14"/>
+      <c r="I4" s="15"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="14" t="s">
+        <v>239</v>
+      </c>
+      <c r="B5" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="13" t="s">
-        <v>251</v>
-      </c>
-      <c r="D5" s="13" t="s">
-        <v>252</v>
-      </c>
-      <c r="E5" s="13" t="s">
+      <c r="C5" s="14" t="s">
+        <v>266</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>267</v>
+      </c>
+      <c r="E5" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="F5" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="G5" s="13"/>
-      <c r="H5" s="13"/>
-      <c r="I5" s="14"/>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="13" t="s">
-        <v>176</v>
-      </c>
-      <c r="B6" s="13" t="s">
+      <c r="F5" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="G5" s="14"/>
+      <c r="H5" s="14"/>
+      <c r="I5" s="15"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="14" t="s">
+        <v>182</v>
+      </c>
+      <c r="B6" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="13" t="s">
-        <v>253</v>
-      </c>
-      <c r="D6" s="13" t="s">
-        <v>254</v>
-      </c>
-      <c r="E6" s="13" t="s">
+      <c r="C6" s="14" t="s">
+        <v>268</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>269</v>
+      </c>
+      <c r="E6" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="F6" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="G6" s="13"/>
-      <c r="H6" s="13"/>
-      <c r="I6" s="14"/>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="13" t="s">
-        <v>255</v>
-      </c>
-      <c r="B7" s="13" t="s">
+      <c r="F6" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="G6" s="14"/>
+      <c r="H6" s="14"/>
+      <c r="I6" s="15"/>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="14" t="s">
+        <v>270</v>
+      </c>
+      <c r="B7" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="13" t="s">
-        <v>256</v>
-      </c>
-      <c r="D7" s="13" t="s">
-        <v>257</v>
-      </c>
-      <c r="E7" s="13" t="s">
+      <c r="C7" s="14" t="s">
+        <v>271</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>272</v>
+      </c>
+      <c r="E7" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="F7" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="G7" s="13"/>
-      <c r="H7" s="13"/>
-      <c r="I7" s="14"/>
-    </row>
-    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="13" t="s">
-        <v>258</v>
-      </c>
-      <c r="B8" s="13" t="s">
+      <c r="F7" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="G7" s="14"/>
+      <c r="H7" s="14"/>
+      <c r="I7" s="15"/>
+    </row>
+    <row r="8" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="14" t="s">
+        <v>273</v>
+      </c>
+      <c r="B8" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="13" t="s">
-        <v>259</v>
-      </c>
-      <c r="D8" s="13" t="s">
-        <v>260</v>
-      </c>
-      <c r="E8" s="13" t="s">
+      <c r="C8" s="14" t="s">
+        <v>274</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>275</v>
+      </c>
+      <c r="E8" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="F8" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="G8" s="13"/>
-      <c r="H8" s="13"/>
-      <c r="I8" s="14"/>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="13" t="s">
-        <v>180</v>
-      </c>
-      <c r="B9" s="13" t="s">
+      <c r="F8" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="G8" s="14"/>
+      <c r="H8" s="14"/>
+      <c r="I8" s="15"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="14" t="s">
+        <v>186</v>
+      </c>
+      <c r="B9" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="13" t="s">
-        <v>261</v>
-      </c>
-      <c r="D9" s="13" t="s">
-        <v>262</v>
-      </c>
-      <c r="E9" s="13" t="s">
+      <c r="C9" s="14" t="s">
+        <v>276</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>277</v>
+      </c>
+      <c r="E9" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="F9" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="G9" s="13"/>
-      <c r="H9" s="13"/>
-      <c r="I9" s="14"/>
-    </row>
-    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="13" t="s">
-        <v>263</v>
-      </c>
-      <c r="B10" s="13" t="s">
+      <c r="F9" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="G9" s="14"/>
+      <c r="H9" s="14"/>
+      <c r="I9" s="15"/>
+    </row>
+    <row r="10" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="14" t="s">
+        <v>278</v>
+      </c>
+      <c r="B10" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="13" t="s">
-        <v>264</v>
-      </c>
-      <c r="D10" s="13" t="s">
-        <v>265</v>
-      </c>
-      <c r="E10" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="F10" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="G10" s="13" t="s">
-        <v>266</v>
-      </c>
-      <c r="H10" s="13"/>
-      <c r="I10" s="14"/>
-    </row>
-    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="13" t="s">
-        <v>267</v>
-      </c>
-      <c r="B11" s="13" t="s">
+      <c r="C10" s="14" t="s">
+        <v>279</v>
+      </c>
+      <c r="D10" s="14" t="s">
+        <v>280</v>
+      </c>
+      <c r="E10" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="F10" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="G10" s="14" t="s">
+        <v>281</v>
+      </c>
+      <c r="H10" s="14"/>
+      <c r="I10" s="15"/>
+    </row>
+    <row r="11" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="14" t="s">
+        <v>282</v>
+      </c>
+      <c r="B11" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="13" t="s">
-        <v>268</v>
-      </c>
-      <c r="D11" s="13" t="s">
-        <v>269</v>
-      </c>
-      <c r="E11" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="F11" s="13" t="s">
+      <c r="C11" s="14" t="s">
+        <v>283</v>
+      </c>
+      <c r="D11" s="14" t="s">
+        <v>284</v>
+      </c>
+      <c r="E11" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="F11" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="G11" s="13" t="s">
-        <v>263</v>
-      </c>
-      <c r="H11" s="13"/>
-      <c r="I11" s="14"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="13" t="s">
-        <v>270</v>
-      </c>
-      <c r="B12" s="13" t="s">
+      <c r="G11" s="14" t="s">
+        <v>278</v>
+      </c>
+      <c r="H11" s="14"/>
+      <c r="I11" s="15"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="14" t="s">
+        <v>285</v>
+      </c>
+      <c r="B12" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C12" s="13" t="s">
-        <v>271</v>
-      </c>
-      <c r="D12" s="13" t="s">
-        <v>272</v>
-      </c>
-      <c r="E12" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="F12" s="13" t="s">
+      <c r="C12" s="14" t="s">
+        <v>286</v>
+      </c>
+      <c r="D12" s="14" t="s">
+        <v>287</v>
+      </c>
+      <c r="E12" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="F12" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="G12" s="13"/>
-      <c r="H12" s="13"/>
-      <c r="I12" s="14"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="13" t="s">
-        <v>203</v>
-      </c>
-      <c r="B13" s="13" t="s">
+      <c r="G12" s="14"/>
+      <c r="H12" s="14"/>
+      <c r="I12" s="15"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="14" t="s">
+        <v>209</v>
+      </c>
+      <c r="B13" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="C13" s="13" t="s">
-        <v>273</v>
-      </c>
-      <c r="D13" s="13" t="s">
-        <v>274</v>
-      </c>
-      <c r="E13" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="F13" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="G13" s="13" t="s">
-        <v>194</v>
-      </c>
-      <c r="H13" s="13"/>
-      <c r="I13" s="14"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="13" t="s">
+      <c r="C13" s="14" t="s">
+        <v>288</v>
+      </c>
+      <c r="D13" s="14" t="s">
+        <v>289</v>
+      </c>
+      <c r="E13" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="F13" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="G13" s="14" t="s">
+        <v>200</v>
+      </c>
+      <c r="H13" s="14"/>
+      <c r="I13" s="15"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="B14" s="13" t="s">
+      <c r="B14" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="C14" s="13" t="s">
-        <v>275</v>
-      </c>
-      <c r="D14" s="13" t="s">
-        <v>276</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="F14" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="G14" s="13" t="s">
-        <v>203</v>
-      </c>
-      <c r="H14" s="13"/>
-      <c r="I14" s="14"/>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="13" t="s">
-        <v>277</v>
-      </c>
-      <c r="B15" s="13" t="s">
+      <c r="C14" s="14" t="s">
+        <v>290</v>
+      </c>
+      <c r="D14" s="14" t="s">
+        <v>291</v>
+      </c>
+      <c r="E14" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="F14" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="G14" s="14" t="s">
+        <v>209</v>
+      </c>
+      <c r="H14" s="14"/>
+      <c r="I14" s="15"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="14" t="s">
+        <v>292</v>
+      </c>
+      <c r="B15" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>278</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>279</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="F15" s="13" t="s">
+      <c r="C15" s="14" t="s">
+        <v>293</v>
+      </c>
+      <c r="D15" s="14" t="s">
+        <v>294</v>
+      </c>
+      <c r="E15" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="F15" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="G15" s="13"/>
-      <c r="H15" s="13"/>
-      <c r="I15" s="14"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="13" t="s">
-        <v>280</v>
-      </c>
-      <c r="B16" s="13" t="s">
+      <c r="G15" s="14"/>
+      <c r="H15" s="14"/>
+      <c r="I15" s="15"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="14" t="s">
+        <v>295</v>
+      </c>
+      <c r="B16" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>281</v>
-      </c>
-      <c r="D16" s="13" t="s">
-        <v>282</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="F16" s="13" t="s">
+      <c r="C16" s="14" t="s">
+        <v>296</v>
+      </c>
+      <c r="D16" s="14" t="s">
+        <v>297</v>
+      </c>
+      <c r="E16" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="F16" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="G16" s="13" t="s">
-        <v>233</v>
-      </c>
-      <c r="H16" s="13"/>
-      <c r="I16" s="14"/>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="13" t="s">
-        <v>221</v>
-      </c>
-      <c r="B17" s="13" t="s">
+      <c r="G16" s="14" t="s">
+        <v>239</v>
+      </c>
+      <c r="H16" s="14"/>
+      <c r="I16" s="15"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="14" t="s">
+        <v>227</v>
+      </c>
+      <c r="B17" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="C17" s="13" t="s">
-        <v>283</v>
-      </c>
-      <c r="D17" s="13" t="s">
-        <v>284</v>
-      </c>
-      <c r="E17" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="F17" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="G17" s="13" t="s">
-        <v>218</v>
-      </c>
-      <c r="H17" s="13"/>
-      <c r="I17" s="14"/>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="13" t="s">
-        <v>285</v>
-      </c>
-      <c r="B18" s="13" t="s">
+      <c r="C17" s="14" t="s">
+        <v>298</v>
+      </c>
+      <c r="D17" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="E17" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="F17" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="G17" s="14" t="s">
+        <v>224</v>
+      </c>
+      <c r="H17" s="14"/>
+      <c r="I17" s="15"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="14" t="s">
+        <v>300</v>
+      </c>
+      <c r="B18" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>286</v>
-      </c>
-      <c r="D18" s="13" t="s">
-        <v>287</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="F18" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="G18" s="13" t="s">
-        <v>221</v>
-      </c>
-      <c r="H18" s="13"/>
-      <c r="I18" s="14"/>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="13" t="s">
+      <c r="C18" s="14" t="s">
+        <v>301</v>
+      </c>
+      <c r="D18" s="14" t="s">
+        <v>302</v>
+      </c>
+      <c r="E18" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="F18" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="G18" s="14" t="s">
+        <v>227</v>
+      </c>
+      <c r="H18" s="14"/>
+      <c r="I18" s="15"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="14" t="s">
         <v>119</v>
       </c>
-      <c r="B19" s="13" t="s">
+      <c r="B19" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="C19" s="13" t="s">
-        <v>288</v>
-      </c>
-      <c r="D19" s="13" t="s">
-        <v>289</v>
-      </c>
-      <c r="E19" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="F19" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="G19" s="13" t="s">
-        <v>222</v>
-      </c>
-      <c r="H19" s="13"/>
-      <c r="I19" s="14"/>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="13" t="s">
-        <v>290</v>
-      </c>
-      <c r="B20" s="13" t="s">
+      <c r="C19" s="14" t="s">
+        <v>303</v>
+      </c>
+      <c r="D19" s="14" t="s">
+        <v>304</v>
+      </c>
+      <c r="E19" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="F19" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="G19" s="14" t="s">
+        <v>228</v>
+      </c>
+      <c r="H19" s="14"/>
+      <c r="I19" s="15"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="14" t="s">
+        <v>305</v>
+      </c>
+      <c r="B20" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>291</v>
-      </c>
-      <c r="D20" s="13" t="s">
-        <v>292</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="F20" s="13" t="s">
+      <c r="C20" s="14" t="s">
+        <v>306</v>
+      </c>
+      <c r="D20" s="14" t="s">
+        <v>307</v>
+      </c>
+      <c r="E20" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="F20" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="G20" s="13" t="s">
+      <c r="G20" s="14" t="s">
         <v>107</v>
       </c>
-      <c r="H20" s="13"/>
-      <c r="I20" s="14"/>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="13" t="s">
-        <v>293</v>
-      </c>
-      <c r="B21" s="13" t="s">
+      <c r="H20" s="14"/>
+      <c r="I20" s="15"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="14" t="s">
+        <v>308</v>
+      </c>
+      <c r="B21" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="C21" s="13" t="s">
-        <v>294</v>
-      </c>
-      <c r="D21" s="13" t="s">
-        <v>295</v>
-      </c>
-      <c r="E21" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="F21" s="13" t="s">
+      <c r="C21" s="14" t="s">
+        <v>309</v>
+      </c>
+      <c r="D21" s="14" t="s">
+        <v>310</v>
+      </c>
+      <c r="E21" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="F21" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="G21" s="13" t="s">
-        <v>218</v>
-      </c>
-      <c r="H21" s="13"/>
-      <c r="I21" s="14"/>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="13" t="s">
-        <v>296</v>
-      </c>
-      <c r="B22" s="13" t="s">
+      <c r="G21" s="14" t="s">
+        <v>224</v>
+      </c>
+      <c r="H21" s="14"/>
+      <c r="I21" s="15"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="14" t="s">
+        <v>311</v>
+      </c>
+      <c r="B22" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>297</v>
-      </c>
-      <c r="D22" s="13" t="s">
-        <v>298</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="F22" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="G22" s="13" t="s">
-        <v>213</v>
-      </c>
-      <c r="H22" s="13"/>
-      <c r="I22" s="14"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="13" t="s">
-        <v>299</v>
-      </c>
-      <c r="B23" s="13" t="s">
+      <c r="C22" s="14" t="s">
+        <v>312</v>
+      </c>
+      <c r="D22" s="14" t="s">
+        <v>313</v>
+      </c>
+      <c r="E22" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="F22" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="G22" s="14" t="s">
+        <v>219</v>
+      </c>
+      <c r="H22" s="14"/>
+      <c r="I22" s="15"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="B23" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>300</v>
-      </c>
-      <c r="D23" s="13" t="s">
-        <v>301</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="F23" s="13" t="s">
+      <c r="C23" s="14" t="s">
+        <v>315</v>
+      </c>
+      <c r="D23" s="14" t="s">
+        <v>316</v>
+      </c>
+      <c r="E23" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="F23" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="G23" s="13" t="s">
-        <v>230</v>
-      </c>
-      <c r="H23" s="13"/>
-      <c r="I23" s="14"/>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="13" t="s">
-        <v>302</v>
-      </c>
-      <c r="B24" s="13" t="s">
+      <c r="G23" s="14" t="s">
+        <v>236</v>
+      </c>
+      <c r="H23" s="14"/>
+      <c r="I23" s="15"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="14" t="s">
+        <v>317</v>
+      </c>
+      <c r="B24" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="C24" s="13" t="s">
-        <v>303</v>
-      </c>
-      <c r="D24" s="13" t="s">
-        <v>304</v>
-      </c>
-      <c r="E24" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="F24" s="13" t="s">
+      <c r="C24" s="14" t="s">
+        <v>318</v>
+      </c>
+      <c r="D24" s="14" t="s">
+        <v>319</v>
+      </c>
+      <c r="E24" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="F24" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="G24" s="13" t="s">
+      <c r="G24" s="14" t="s">
         <v>137</v>
       </c>
-      <c r="H24" s="13"/>
-      <c r="I24" s="14"/>
-    </row>
-    <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="13" t="s">
-        <v>305</v>
-      </c>
-      <c r="B25" s="13" t="s">
+      <c r="H24" s="14"/>
+      <c r="I24" s="15"/>
+    </row>
+    <row r="25" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="14" t="s">
+        <v>320</v>
+      </c>
+      <c r="B25" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="C25" s="13" t="s">
-        <v>306</v>
-      </c>
-      <c r="D25" s="13" t="s">
-        <v>307</v>
-      </c>
-      <c r="E25" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="F25" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="G25" s="13" t="s">
-        <v>221</v>
-      </c>
-      <c r="H25" s="13"/>
-      <c r="I25" s="14"/>
+      <c r="C25" s="14" t="s">
+        <v>321</v>
+      </c>
+      <c r="D25" s="14" t="s">
+        <v>322</v>
+      </c>
+      <c r="E25" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="F25" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="G25" s="14" t="s">
+        <v>227</v>
+      </c>
+      <c r="H25" s="14"/>
+      <c r="I25" s="15"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:I25"/>
